--- a/juop_data.xlsx
+++ b/juop_data.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F112"/>
+  <dimension ref="A1:F116"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col width="33.44140625" customWidth="1" style="10" min="1" max="1"/>
@@ -3734,6 +3734,114 @@
       <c r="F112" t="inlineStr">
         <is>
           <t>GM-435638</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>GM-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>0/0</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>GM-</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Smart</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>06/02/2026</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>San NIcolas</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>5/0</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>GM-12334</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>PLDT</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Lemery</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>6/4</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>GM-567654</t>
         </is>
       </c>
     </row>
